--- a/output/pdf_financials_xlsx/JJ.xlsx
+++ b/output/pdf_financials_xlsx/JJ.xlsx
@@ -828,22 +828,22 @@
         <v>1.309221</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04578</v>
+        <v>0.294406</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.198288</v>
+        <v>0.249823</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.225927</v>
+        <v>0.265616</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.192855</v>
+        <v>0.229376</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.080891</v>
+        <v>0.08912399999999999</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.250332</v>
+        <v>0.250352</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0.520254</v>
@@ -5077,40 +5077,40 @@
         <v>3.248274</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.656296</v>
+        <v>0.166249</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.662088</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.769672</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.777478</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.988435</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.337109</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.52039</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.754121</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.775009</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.060919</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.151363</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.485831</v>
       </c>
     </row>
     <row r="93">
@@ -9696,7 +9696,11 @@
           <t>Reserves (notes 10 and 15)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11726,7 +11730,11 @@
           <t>Reserves (notes 10 and 14)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -12578,7 +12586,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -13354,7 +13366,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15104,7 +15120,11 @@
           <t>Reserves (note 12) 702,010</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -34050,7 +34070,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JJ.xlsx
+++ b/output/pdf_financials_xlsx/JJ.xlsx
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000424</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002014</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.065393</v>
+        <v>-3.065817</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.058096</v>
+        <v>-3.06011</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-6.158137</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.065393</v>
+        <v>-3.065817</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.058096</v>
+        <v>-3.06011</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-6.158137</v>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1084.572736664827</v>
+        <v>-1084.722752940177</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-588.8575021133121</v>
+        <v>-589.2453117207463</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-220.4465536393098</v>
@@ -47552,7 +47552,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">

--- a/output/pdf_financials_xlsx/JJ.xlsx
+++ b/output/pdf_financials_xlsx/JJ.xlsx
@@ -546,15 +546,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.45</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0.282636</v>
@@ -599,15 +595,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -652,15 +644,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.45</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0.282636</v>
@@ -705,15 +693,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.781758</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.872394</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.706947</v>
@@ -758,15 +742,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -811,15 +791,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>2.791813</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2.024927</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>2.055251</v>
@@ -864,15 +840,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>3.952256</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>3.592303</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3.594535</v>
@@ -917,15 +889,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-3.214822</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-2.825779</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0.579111</v>
@@ -970,15 +938,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.104235</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.055165</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.000424</v>
@@ -1023,15 +987,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1076,15 +1036,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1129,15 +1085,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-0.006885</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.015129</v>
@@ -1211,7 +1163,7 @@
         <v>-1.670588</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-3.829763</v>
+        <v>-3.794398</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-6.555039</v>
@@ -1220,13 +1172,13 @@
         <v>-5.123052</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-3.278196</v>
+        <v>-2.950014</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-1.358341</v>
+        <v>-0.691248</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-7.562396</v>
+        <v>-7.406838</v>
       </c>
     </row>
     <row r="17">
@@ -1235,15 +1187,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1264,7 +1212,7 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.035365</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1273,13 +1221,13 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.328182</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.667093</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.155558</v>
       </c>
     </row>
     <row r="18">
@@ -1495,15 +1443,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1548,15 +1492,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1654,15 +1594,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.02</v>
@@ -1707,15 +1643,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.02</v>
@@ -1844,7 +1776,7 @@
         <v>-1.670588</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.829763</v>
+        <v>-3.794398</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-6.555039</v>
@@ -1853,13 +1785,13 @@
         <v>-5.123052</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.278196</v>
+        <v>-2.950014</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.358341</v>
+        <v>-0.691248</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-7.562396</v>
+        <v>-7.406838</v>
       </c>
     </row>
     <row r="28">
@@ -1868,15 +1800,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1950,7 +1878,7 @@
         <v>-1.670588</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.829763</v>
+        <v>-3.794398</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-6.555039</v>
@@ -1959,13 +1887,13 @@
         <v>-5.123052</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.278196</v>
+        <v>-2.950014</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.358341</v>
+        <v>-0.691248</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.562396</v>
+        <v>-7.406838</v>
       </c>
     </row>
     <row r="30">
@@ -2003,7 +1931,7 @@
         <v>-76.71538598595546</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-626.5440440276678</v>
+        <v>-620.7583778866981</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-1561.656847306366</v>
@@ -2012,13 +1940,13 @@
         <v>-357.9500006987046</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-158.973127970566</v>
+        <v>-143.0582409157236</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-62.73449096674614</v>
+        <v>-31.92504048083753</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-463.8744059258968</v>
+        <v>-454.3325391898755</v>
       </c>
     </row>
     <row r="31">
@@ -2056,7 +1984,7 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.9320319059835053</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -2065,13 +1993,13 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.12476076384722</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-96.50559567622619</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.100194441946753</v>
       </c>
     </row>
     <row r="32">
@@ -3835,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.096135</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -5928,7 +5856,7 @@
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>1.2697</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -6105,10 +6033,10 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005805</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00537</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -6129,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008666999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6415,16 +6343,16 @@
         <v>0</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.176972</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.220296</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.115601</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07498</v>
       </c>
     </row>
     <row r="117">
@@ -7480,10 +7408,10 @@
         </is>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005805</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00537</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -7504,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008666999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7539,10 +7467,10 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.650475</v>
+        <v>-1.65628</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-2.247167</v>
+        <v>-2.252537</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-1.484628</v>
@@ -7563,7 +7491,7 @@
         <v>-3.988996</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-6.105828</v>
+        <v>-6.114495</v>
       </c>
     </row>
   </sheetData>
@@ -7577,7 +7505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R508"/>
+  <dimension ref="A1:R548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19364,7 +19292,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -19444,7 +19376,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -23796,7 +23732,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -26518,7 +26458,11 @@
           <t>Impairment loss on goodwill</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -27183,15 +27127,11 @@
           <t>TotalRevenue</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E237" s="5" t="n">
+        <v>0.737434</v>
+      </c>
+      <c r="F237" s="5" t="n">
+        <v>0.766524</v>
       </c>
       <c r="G237" s="5" t="n">
         <v>0.579111</v>
@@ -27803,15 +27743,11 @@
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E245" s="5" t="n">
+        <v>0.117088</v>
+      </c>
+      <c r="F245" s="5" t="n">
+        <v>0.170703</v>
       </c>
       <c r="G245" s="5" t="n">
         <v>0.190177</v>
@@ -27871,15 +27807,11 @@
           <t>OtherOperatingExpenses</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E246" s="5" t="n">
+        <v>0.395182</v>
+      </c>
+      <c r="F246" s="5" t="n">
+        <v>0.140946</v>
       </c>
       <c r="G246" s="5" t="n">
         <v>0.146536</v>
@@ -27935,15 +27867,11 @@
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E247" s="5" t="n">
+        <v>0.109633</v>
+      </c>
+      <c r="F247" s="5" t="n">
+        <v>0.119891</v>
       </c>
       <c r="G247" s="5" t="n">
         <v>0.103944</v>
@@ -28003,15 +27931,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E248" s="5" t="n">
+        <v>0.011642</v>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>0.010584</v>
       </c>
       <c r="G248" s="5" t="n">
         <v>0.011326</v>
@@ -28076,10 +28000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F249" s="5" t="n">
+        <v>-0.006885</v>
       </c>
       <c r="G249" s="5" t="n">
         <v>0.015129</v>
@@ -28315,15 +28237,11 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E252" s="5" t="n">
+        <v>3.952256</v>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>3.592303</v>
       </c>
       <c r="G252" s="5" t="n">
         <v>3.594535</v>
@@ -29008,7 +28926,11 @@
           <t>Deferred income tax recovery (note 18)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -29255,15 +29177,11 @@
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E264" s="5" t="n">
+        <v>106.473997</v>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>108.190641</v>
       </c>
       <c r="G264" s="5" t="n">
         <v>140.026757</v>
@@ -36226,7 +36144,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -42665,15 +42587,11 @@
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E422" s="5" t="n">
+        <v>0.737434</v>
+      </c>
+      <c r="F422" s="5" t="n">
+        <v>0.316524</v>
       </c>
       <c r="G422" s="5" t="n">
         <v>0.296475</v>
@@ -46589,15 +46507,11 @@
           <t>TotalRevenue</t>
         </is>
       </c>
-      <c r="E468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E468" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F468" s="5" t="n">
+        <v>0.45</v>
       </c>
       <c r="G468" s="5" t="n">
         <v>0.282636</v>
@@ -46855,15 +46769,11 @@
           <t>Amortization</t>
         </is>
       </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E471" s="5" t="n">
+        <v>0.255195</v>
+      </c>
+      <c r="F471" s="5" t="n">
+        <v>0.220414</v>
       </c>
       <c r="G471" s="5" t="n">
         <v>0.155999</v>
@@ -46939,20 +46849,14 @@
         </is>
       </c>
       <c r="D472" t="inlineStr"/>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E472" s="5" t="n">
+        <v>0.081844</v>
+      </c>
+      <c r="F472" s="5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="G472" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H472" s="5" t="n">
         <v>0.330603</v>
@@ -47029,15 +46933,11 @@
           <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E473" s="5" t="n">
+        <v>0.124476</v>
+      </c>
+      <c r="F473" s="5" t="n">
+        <v>0.190559</v>
       </c>
       <c r="G473" s="5" t="n">
         <v>0.367088</v>
@@ -47291,15 +47191,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E476" s="5" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="F476" s="5" t="n">
+        <v>0.499627</v>
       </c>
       <c r="G476" s="5" t="n">
         <v>0.334604</v>
@@ -47379,15 +47275,11 @@
           <t>OtherOperatingExpenses</t>
         </is>
       </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E477" s="5" t="n">
+        <v>2.396631</v>
+      </c>
+      <c r="F477" s="5" t="n">
+        <v>1.883981</v>
       </c>
       <c r="G477" s="5" t="n">
         <v>1.908715</v>
@@ -47467,15 +47359,11 @@
           <t>OperatingIncome</t>
         </is>
       </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E478" s="5" t="n">
+        <v>-3.214822</v>
+      </c>
+      <c r="F478" s="5" t="n">
+        <v>-2.825779</v>
       </c>
       <c r="G478" s="5" t="n">
         <v>-3.015424</v>
@@ -47555,15 +47443,11 @@
           <t>InterestIncomeNonOperating</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E479" s="5" t="n">
+        <v>0.104235</v>
+      </c>
+      <c r="F479" s="5" t="n">
+        <v>0.055165</v>
       </c>
       <c r="G479" s="5" t="n">
         <v>0.000424</v>
@@ -47734,10 +47618,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F481" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G481" s="5" t="n">
         <v>-0.025755</v>
@@ -48071,15 +47953,11 @@
         </is>
       </c>
       <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E485" s="5" t="n">
+        <v>0.135312</v>
+      </c>
+      <c r="F485" s="5" t="n">
+        <v>0.051758</v>
       </c>
       <c r="G485" s="5" t="n">
         <v>-0.049969</v>
@@ -48248,10 +48126,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F487" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G487" s="5" t="n">
         <v>0.0101</v>
@@ -48426,10 +48302,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F489" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="G489" s="5" t="n">
         <v>-2e-08</v>
@@ -50125,6 +49999,3380 @@
         </is>
       </c>
       <c r="R508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Management fees (note 12(b))</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F509" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G509" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Shareholder communication</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E510" s="5" t="n">
+        <v>0.001716</v>
+      </c>
+      <c r="F510" s="5" t="n">
+        <v>0.002183</v>
+      </c>
+      <c r="G510" s="5" t="n">
+        <v>0.001017</v>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Write-off of equipment</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
+      <c r="E511" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F511" s="5" t="n">
+        <v>-0.003407</v>
+      </c>
+      <c r="G511" s="5" t="n">
+        <v>-0.000261</v>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Loss on sale of equipment</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F512" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G512" s="5" t="n">
+        <v>-0.024377</v>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Net Loss for Year</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" s="5" t="n">
+        <v>-3.07951</v>
+      </c>
+      <c r="F513" s="5" t="n">
+        <v>-2.774021</v>
+      </c>
+      <c r="G513" s="5" t="n">
+        <v>-2.903227</v>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable securities</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F514" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="G514" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Transfer of unrealized loss upon sale of marketable</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Comprehensive Loss for Year $</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F515" s="5" t="n">
+        <v>-2.784121</v>
+      </c>
+      <c r="G515" s="5" t="n">
+        <v>-2.893127</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Shares       Amount          Deficit       Warrants     Surplus        Loss           Equity</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2008 107,149,545 $ 31,069,593 $ (30,439,608) $ 50,000 $ 3,194,128 $</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr"/>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F516" s="5" t="n">
+        <v>3.874113</v>
+      </c>
+      <c r="G516" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Shares       Amount          Deficit       Warrants     Surplus        Loss           Equity</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Net loss for year 0 0 (2,774,021) 0 0</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F517" s="5" t="n">
+        <v>-2.774021</v>
+      </c>
+      <c r="G517" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Shares       Amount          Deficit       Warrants     Surplus        Loss           Equity</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Shares issued for cash 10,000,000 150,000 0 0 0</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F518" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G518" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Shares       Amount          Deficit       Warrants     Surplus        Loss           Equity</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Transfer on expiry of warrants 0 0 0 (50,000) 50,000</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G519" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable securities 0 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F520" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="G520" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 0 0 0 0 4,146</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F521" s="5" t="n">
+        <v>0.004146</v>
+      </c>
+      <c r="G521" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2009 117,149,545 31,219,593 (33,213,629) 0 3,248,274</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F522" s="5" t="n">
+        <v>1.244138</v>
+      </c>
+      <c r="G522" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Net loss for year 0 0 (2,903,227) 0 0</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F523" s="5" t="n">
+        <v>-2.903227</v>
+      </c>
+      <c r="G523" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>placement, net of share</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>placement, net of share issuance costs 54,390,000 1,357,394 0 1,203,386 0</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F524" s="5" t="n">
+        <v>2.56078</v>
+      </c>
+      <c r="G524" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>placement, net of share</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Exercise of options 226,000 22,600 0 0 0</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F525" s="5" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="G525" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>surplus on exercise of</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>surplus on exercise of options 0 12,342 0 0 (12,342)</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F526" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>upon sale of marketable</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>upon sale of marketable securities 0 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr"/>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F527" s="5" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="G527" s="5" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>upon sale of marketable</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 0 0 0 0 420,364</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F528" s="5" t="n">
+        <v>0.420364</v>
+      </c>
+      <c r="G528" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>upon sale of marketable</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2010 171,765,545 $ 32,611,929 $ (36,116,856) $ 1,203,386 $ 3,656,296 $</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr"/>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F529" s="5" t="n">
+        <v>1.354755</v>
+      </c>
+      <c r="G529" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E530" s="5" t="n">
+        <v>-0.309551</v>
+      </c>
+      <c r="F530" s="5" t="n">
+        <v>-0.006885</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Management fees (note 11(b))</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E531" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F531" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Gain on sale of domain name</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr"/>
+      <c r="E532" s="5" t="n">
+        <v>0.031077</v>
+      </c>
+      <c r="F532" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Loss</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable securities</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F533" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Loss</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Comprehensive Loss for Year $</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" s="5" t="n">
+        <v>-3.07951</v>
+      </c>
+      <c r="F534" s="5" t="n">
+        <v>-2.784121</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Loss</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Basic and Diluted Loss Per Share $</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E535" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F535" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Shares       Amount          Deficit       Warrants     Surplus   Subscriptions     Loss          Equity</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2007 102,070,795 $ 30,253,288 $ (27,360,098) $ 0 $ 3,159,311 $ 850,000 $</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" s="5" t="n">
+        <v>6.902501</v>
+      </c>
+      <c r="F536" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Shares       Amount          Deficit       Warrants     Surplus   Subscriptions     Loss          Equity</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Net loss for year 0 0 (3,079,510) 0 0 0</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" s="5" t="n">
+        <v>-3.07951</v>
+      </c>
+      <c r="F537" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Shares issued for cash</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Exercise of options 78,750 9,200 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" s="5" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F538" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Shares issued for cash</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Share subscriptions 5,000,000 800,000 0 50,000 0 (850,000)</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F539" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>surplus on exercise of</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>surplus on exercise of options 0 7,105 0 0 (7,105) 0</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F540" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>surplus on exercise of</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 0 0 0 0 41,922 0</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr"/>
+      <c r="E541" s="5" t="n">
+        <v>0.041922</v>
+      </c>
+      <c r="F541" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>surplus on exercise of</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2008 107,149,545 31,069,593 (30,439,608) 50,000 3,194,128 0</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" s="5" t="n">
+        <v>3.874113</v>
+      </c>
+      <c r="F542" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>surplus on exercise of</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Net loss for year 0 0 (2,774,021) 0 0 0</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" s="5" t="n">
+        <v>-2.774021</v>
+      </c>
+      <c r="F543" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>surplus on exercise of</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Shares issued for cash 10,000,000 150,000 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F544" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>surplus on exercise of</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Transfer on expiry of warrants 0 0 0 (50,000) 50,000 0</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F545" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable securities 0 0 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="F546" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 0 0 0 0 4,146 0</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" s="5" t="n">
+        <v>0.004146</v>
+      </c>
+      <c r="F547" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2009 117,149,545 $ 31,219,593 $ (33,213,629) $ 0 $ 3,248,274 $ 0 $</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" s="5" t="n">
+        <v>1.244138</v>
+      </c>
+      <c r="F548" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
         <is>
           <t>-</t>
         </is>
